--- a/outputs/Block2_ML_Predictions_v12.xlsx
+++ b/outputs/Block2_ML_Predictions_v12.xlsx
@@ -618,31 +618,31 @@
         <v>57</v>
       </c>
       <c r="C2">
-        <v>0.5015439999999998</v>
+        <v>0.5025559999999998</v>
       </c>
       <c r="D2">
-        <v>0.4872199999999994</v>
+        <v>0.4879279999999993</v>
       </c>
       <c r="E2">
-        <v>0.487434430017597</v>
+        <v>0.4850537176443364</v>
       </c>
       <c r="F2">
         <v>0.4868</v>
       </c>
       <c r="G2">
-        <v>0.4953563430886915</v>
+        <v>0.4962370216909646</v>
       </c>
       <c r="H2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="I2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="J2" t="s">
         <v>7</v>
       </c>
       <c r="K2">
-        <v>0.5093213701657459</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="L2">
         <v>0.01323492690170848</v>
@@ -665,31 +665,31 @@
         <v>57</v>
       </c>
       <c r="C3">
-        <v>0.4696599999999989</v>
+        <v>0.4686639999999987</v>
       </c>
       <c r="D3">
-        <v>0.4840119999999993</v>
+        <v>0.4831359999999993</v>
       </c>
       <c r="E3">
-        <v>0.485114447962659</v>
+        <v>0.4848653204771308</v>
       </c>
       <c r="F3">
         <v>0.484</v>
       </c>
       <c r="G3">
-        <v>0.4758597523032031</v>
+        <v>0.4749155896970425</v>
       </c>
       <c r="H3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="I3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="J3" t="s">
         <v>7</v>
       </c>
       <c r="K3">
-        <v>0.4614786298342541</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="L3">
         <v>0.01064148394560983</v>
@@ -712,25 +712,25 @@
         <v>58</v>
       </c>
       <c r="C4">
-        <v>1.092</v>
+        <v>1.128</v>
       </c>
       <c r="D4">
-        <v>1.224</v>
+        <v>1.252</v>
       </c>
       <c r="E4">
-        <v>0.5513716620292705</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="F4">
         <v>1.4</v>
       </c>
       <c r="G4">
-        <v>1.155708792388448</v>
+        <v>1.187847653455815</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>0.5513716620292705</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="L4">
         <v>0.8200692764238203</v>
@@ -753,25 +753,25 @@
         <v>58</v>
       </c>
       <c r="C5">
-        <v>1.276</v>
+        <v>1.412</v>
       </c>
       <c r="D5">
-        <v>1.788</v>
+        <v>1.808</v>
       </c>
       <c r="E5">
-        <v>0.7074963699328916</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="F5">
         <v>2.2</v>
       </c>
       <c r="G5">
-        <v>1.523112891688526</v>
+        <v>1.603126377165344</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>0.7074963699328916</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="L5">
         <v>1.746417103282563</v>
@@ -794,25 +794,25 @@
         <v>58</v>
       </c>
       <c r="C6">
-        <v>7.9</v>
+        <v>7.968</v>
       </c>
       <c r="D6">
-        <v>8.827999999999999</v>
+        <v>8.868</v>
       </c>
       <c r="E6">
-        <v>7.820194910667125</v>
+        <v>10.0582691946606</v>
       </c>
       <c r="F6">
         <v>9.4</v>
       </c>
       <c r="G6">
-        <v>8.347892116185454</v>
+        <v>8.402378129921239</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>7.820194910667125</v>
+        <v>10.0582691946606</v>
       </c>
       <c r="L6">
         <v>4.467028425282805</v>
@@ -835,25 +835,25 @@
         <v>58</v>
       </c>
       <c r="C7">
-        <v>3.516</v>
+        <v>3.54</v>
       </c>
       <c r="D7">
-        <v>4.924</v>
+        <v>4.812</v>
       </c>
       <c r="E7">
-        <v>5.173756282914196</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7">
-        <v>4.195560452143448</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>5.173756282914196</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="L7">
         <v>2.262338789582505</v>
@@ -876,25 +876,25 @@
         <v>58</v>
       </c>
       <c r="C8">
-        <v>13.792</v>
+        <v>13.58</v>
       </c>
       <c r="D8">
-        <v>14.964</v>
+        <v>14.788</v>
       </c>
       <c r="E8">
-        <v>18.4418098343119</v>
+        <v>19.01148659179185</v>
       </c>
       <c r="F8">
         <v>14.6</v>
       </c>
       <c r="G8">
-        <v>14.35765685363077</v>
+        <v>14.16303197882762</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>18.4418098343119</v>
+        <v>19.01148659179185</v>
       </c>
       <c r="L8">
         <v>5.333756871724871</v>
@@ -917,25 +917,25 @@
         <v>58</v>
       </c>
       <c r="C9">
-        <v>2.568</v>
+        <v>3.184</v>
       </c>
       <c r="D9">
-        <v>3.732</v>
+        <v>4.004</v>
       </c>
       <c r="E9">
-        <v>-3.223234081728676</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="F9">
         <v>5.8</v>
       </c>
       <c r="G9">
-        <v>3.129795714698134</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="L9">
         <v>7.059923274159115</v>
@@ -958,25 +958,25 @@
         <v>58</v>
       </c>
       <c r="C10">
-        <v>173.312</v>
+        <v>172.984</v>
       </c>
       <c r="D10">
-        <v>170.552</v>
+        <v>170.488</v>
       </c>
       <c r="E10">
-        <v>176.0063243272117</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="F10">
         <v>169.2</v>
       </c>
       <c r="G10">
-        <v>171.9799070682415</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>176.0063243272117</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="L10">
         <v>4.764861070548267</v>
@@ -999,25 +999,25 @@
         <v>58</v>
       </c>
       <c r="C11">
-        <v>3.096</v>
+        <v>3.948</v>
       </c>
       <c r="D11">
-        <v>4.516</v>
+        <v>4.92</v>
       </c>
       <c r="E11">
-        <v>-5.436536811828134</v>
+        <v>1.16567981478854</v>
       </c>
       <c r="F11">
         <v>7.4</v>
       </c>
       <c r="G11">
-        <v>3.781352160542397</v>
+        <v>4.417128380314937</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1.16567981478854</v>
       </c>
       <c r="L11">
         <v>9.933150479214353</v>
@@ -1040,25 +1040,25 @@
         <v>58</v>
       </c>
       <c r="C12">
-        <v>3.732</v>
+        <v>3.692</v>
       </c>
       <c r="D12">
         <v>3.192</v>
       </c>
       <c r="E12">
-        <v>3.990456585529889</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3.471373122047258</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>3.990456585529889</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="L12">
         <v>0.887818750560327</v>
@@ -1081,25 +1081,25 @@
         <v>58</v>
       </c>
       <c r="C13">
-        <v>1.88</v>
+        <v>1.832</v>
       </c>
       <c r="D13">
-        <v>1.824</v>
+        <v>1.772</v>
       </c>
       <c r="E13">
-        <v>3.02590709890818</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="F13">
         <v>1.6</v>
       </c>
       <c r="G13">
-        <v>1.852972027471568</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>3.02590709890818</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="L13">
         <v>1.198624596172324</v>
@@ -1122,25 +1122,25 @@
         <v>58</v>
       </c>
       <c r="C14">
-        <v>13.488</v>
+        <v>13.316</v>
       </c>
       <c r="D14">
-        <v>12.544</v>
+        <v>12.472</v>
       </c>
       <c r="E14">
-        <v>15.02106749310035</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="F14">
         <v>11.8</v>
       </c>
       <c r="G14">
-        <v>13.03238560594928</v>
+        <v>12.9086498426072</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>15.02106749310035</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="L14">
         <v>3.125306797245826</v>
@@ -1163,25 +1163,25 @@
         <v>58</v>
       </c>
       <c r="C15">
-        <v>8.456</v>
+        <v>8.612</v>
       </c>
       <c r="D15">
-        <v>6.348</v>
+        <v>6.564</v>
       </c>
       <c r="E15">
-        <v>4.233012499265572</v>
+        <v>3.808811132083866</v>
       </c>
       <c r="F15">
         <v>6.6</v>
       </c>
       <c r="G15">
-        <v>7.438589891251147</v>
+        <v>7.623548433245896</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>4.233012499265572</v>
+        <v>3.808811132083866</v>
       </c>
       <c r="L15">
         <v>4.673523904256721</v>
@@ -1204,25 +1204,25 @@
         <v>58</v>
       </c>
       <c r="C16">
-        <v>15.112</v>
+        <v>15.048</v>
       </c>
       <c r="D16">
-        <v>15.028</v>
+        <v>14.824</v>
       </c>
       <c r="E16">
-        <v>17.90152433308469</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="F16">
         <v>14.2</v>
       </c>
       <c r="G16">
-        <v>15.07145804120735</v>
+        <v>14.93988810988627</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>17.90152433308469</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="L16">
         <v>6.129350049043507</v>
@@ -1245,25 +1245,25 @@
         <v>58</v>
       </c>
       <c r="C17">
-        <v>7.252</v>
+        <v>7.352</v>
       </c>
       <c r="D17">
-        <v>5.608</v>
+        <v>5.764</v>
       </c>
       <c r="E17">
-        <v>4.766317009415515</v>
+        <v>4.801946011202828</v>
       </c>
       <c r="F17">
         <v>5.8</v>
       </c>
       <c r="G17">
-        <v>6.458535949343873</v>
+        <v>6.585563921872306</v>
       </c>
       <c r="J17" t="s">
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.766317009415515</v>
+        <v>4.801946011202828</v>
       </c>
       <c r="L17">
         <v>3.997862832988686</v>
@@ -1286,25 +1286,25 @@
         <v>58</v>
       </c>
       <c r="C18">
-        <v>173.296</v>
+        <v>172.1</v>
       </c>
       <c r="D18">
-        <v>175.72</v>
+        <v>175.156</v>
       </c>
       <c r="E18">
-        <v>182.3239848953666</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="F18">
         <v>172.6</v>
       </c>
       <c r="G18">
-        <v>174.4659250965879</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="J18" t="s">
         <v>4</v>
       </c>
       <c r="K18">
-        <v>182.3239848953666</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="L18">
         <v>24.70132137894479</v>
@@ -1327,25 +1327,25 @@
         <v>58</v>
       </c>
       <c r="C19">
-        <v>5.232</v>
+        <v>5.304</v>
       </c>
       <c r="D19">
-        <v>4.208</v>
+        <v>4.316</v>
       </c>
       <c r="E19">
-        <v>3.696547591818899</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="F19">
         <v>4.4</v>
       </c>
       <c r="G19">
-        <v>4.737774216622949</v>
+        <v>4.827149341819798</v>
       </c>
       <c r="J19" t="s">
         <v>4</v>
       </c>
       <c r="K19">
-        <v>3.696547591818899</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="L19">
         <v>2.858585552684069</v>
@@ -1368,25 +1368,25 @@
         <v>59</v>
       </c>
       <c r="C20">
-        <v>0.412</v>
+        <v>0.368</v>
       </c>
       <c r="D20">
-        <v>0.552</v>
+        <v>0.512</v>
       </c>
       <c r="E20">
-        <v>1.125104248703698</v>
+        <v>0.8003007397713651</v>
       </c>
       <c r="F20">
         <v>0.4</v>
       </c>
       <c r="G20">
-        <v>0.4778035103753786</v>
+        <v>0.4356836106718179</v>
       </c>
       <c r="J20" t="s">
         <v>4</v>
       </c>
       <c r="K20">
-        <v>1.125104248703698</v>
+        <v>0.8003007397713651</v>
       </c>
       <c r="L20">
         <v>0.8079772006265793</v>
@@ -1409,25 +1409,25 @@
         <v>59</v>
       </c>
       <c r="C21">
-        <v>0.216</v>
+        <v>0.236</v>
       </c>
       <c r="D21">
-        <v>0.18</v>
+        <v>0.184</v>
       </c>
       <c r="E21">
-        <v>0.01190808928740122</v>
+        <v>-0.05756181698960205</v>
       </c>
       <c r="F21">
         <v>0.2</v>
       </c>
       <c r="G21">
-        <v>0.1990790973320455</v>
+        <v>0.2115586961462879</v>
       </c>
       <c r="J21" t="s">
         <v>4</v>
       </c>
       <c r="K21">
-        <v>0.01190808928740122</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>0.421748166646455</v>
@@ -1450,25 +1450,25 @@
         <v>59</v>
       </c>
       <c r="C22">
-        <v>1.124</v>
+        <v>1.164</v>
       </c>
       <c r="D22">
-        <v>1.364</v>
+        <v>1.34</v>
       </c>
       <c r="E22">
-        <v>1.289478939532622</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="F22">
         <v>1.4</v>
       </c>
       <c r="G22">
-        <v>1.236806017786363</v>
+        <v>1.246724413043333</v>
       </c>
       <c r="J22" t="s">
         <v>4</v>
       </c>
       <c r="K22">
-        <v>1.289478939532622</v>
+        <v>1.234402433809649</v>
       </c>
       <c r="L22">
         <v>0.9319718387197466</v>
@@ -1491,25 +1491,25 @@
         <v>59</v>
       </c>
       <c r="C23">
-        <v>0.66</v>
+        <v>0.612</v>
       </c>
       <c r="D23">
-        <v>0.756</v>
+        <v>0.732</v>
       </c>
       <c r="E23">
-        <v>0.8217382316493707</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="F23">
         <v>0.6</v>
       </c>
       <c r="G23">
-        <v>0.7051224071145452</v>
+        <v>0.6684030088931816</v>
       </c>
       <c r="J23" t="s">
         <v>4</v>
       </c>
       <c r="K23">
-        <v>0.8217382316493707</v>
+        <v>0.3293773794100608</v>
       </c>
       <c r="L23">
         <v>1.559831022862906</v>
@@ -1532,25 +1532,25 @@
         <v>59</v>
       </c>
       <c r="C24">
-        <v>1.868</v>
+        <v>1.9</v>
       </c>
       <c r="D24">
-        <v>1.492</v>
+        <v>1.54</v>
       </c>
       <c r="E24">
-        <v>1.186511751275934</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="F24">
         <v>1.6</v>
       </c>
       <c r="G24">
-        <v>1.691270572134697</v>
+        <v>1.730790973320455</v>
       </c>
       <c r="J24" t="s">
         <v>4</v>
       </c>
       <c r="K24">
-        <v>1.186511751275934</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="L24">
         <v>1.157976831184469</v>
@@ -1573,25 +1573,25 @@
         <v>59</v>
       </c>
       <c r="C25">
-        <v>0.652</v>
+        <v>0.676</v>
       </c>
       <c r="D25">
         <v>0.612</v>
       </c>
       <c r="E25">
-        <v>0.2977289224579263</v>
+        <v>-0.005331174175850051</v>
       </c>
       <c r="F25">
         <v>0.6</v>
       </c>
       <c r="G25">
-        <v>0.633198997035606</v>
+        <v>0.6459183952569697</v>
       </c>
       <c r="J25" t="s">
         <v>4</v>
       </c>
       <c r="K25">
-        <v>0.2977289224579263</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>1.005444112310955</v>
@@ -1614,25 +1614,25 @@
         <v>59</v>
       </c>
       <c r="C26">
-        <v>13.152</v>
+        <v>13.232</v>
       </c>
       <c r="D26">
-        <v>12.22</v>
+        <v>12.328</v>
       </c>
       <c r="E26">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="F26">
         <v>12.4</v>
       </c>
       <c r="G26">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="J26" t="s">
         <v>4</v>
       </c>
       <c r="K26">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="L26">
         <v>2.351026032651849</v>
@@ -1655,25 +1655,25 @@
         <v>59</v>
       </c>
       <c r="C27">
-        <v>1.58</v>
+        <v>1.736</v>
       </c>
       <c r="D27">
-        <v>1.896</v>
+        <v>1.98</v>
       </c>
       <c r="E27">
-        <v>-0.7504271689963384</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="F27">
         <v>2.4</v>
       </c>
       <c r="G27">
-        <v>1.728527923418711</v>
+        <v>1.850686118082802</v>
       </c>
       <c r="J27" t="s">
         <v>4</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="L27">
         <v>1.736334852416627</v>
@@ -1696,25 +1696,25 @@
         <v>59</v>
       </c>
       <c r="C28">
-        <v>0.192</v>
+        <v>0.164</v>
       </c>
       <c r="D28">
-        <v>0.3</v>
+        <v>0.268</v>
       </c>
       <c r="E28">
-        <v>0.851191504820574</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="F28">
         <v>0.2</v>
       </c>
       <c r="G28">
-        <v>0.2427627080038635</v>
+        <v>0.2128826077074241</v>
       </c>
       <c r="J28" t="s">
         <v>4</v>
       </c>
       <c r="K28">
-        <v>0.851191504820574</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="L28">
         <v>0.4925498319332764</v>
@@ -1737,25 +1737,25 @@
         <v>59</v>
       </c>
       <c r="C29">
-        <v>0.656</v>
+        <v>0.632</v>
       </c>
       <c r="D29">
-        <v>0.384</v>
+        <v>0.416</v>
       </c>
       <c r="E29">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F29">
         <v>0.4</v>
       </c>
       <c r="G29">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J29" t="s">
         <v>4</v>
       </c>
       <c r="K29">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L29">
         <v>0.7620693762924241</v>
@@ -1819,25 +1819,25 @@
         <v>59</v>
       </c>
       <c r="C31">
-        <v>0.736</v>
+        <v>0.716</v>
       </c>
       <c r="D31">
-        <v>0.672</v>
+        <v>0.66</v>
       </c>
       <c r="E31">
-        <v>1.081403752400103</v>
+        <v>0.9608490161719081</v>
       </c>
       <c r="F31">
         <v>0.6</v>
       </c>
       <c r="G31">
-        <v>0.7059183952569696</v>
+        <v>0.6896785958498485</v>
       </c>
       <c r="J31" t="s">
         <v>4</v>
       </c>
       <c r="K31">
-        <v>1.081403752400103</v>
+        <v>0.9608490161719081</v>
       </c>
       <c r="L31">
         <v>0.3332002265469857</v>
@@ -1860,25 +1860,25 @@
         <v>59</v>
       </c>
       <c r="C32">
-        <v>1.148</v>
+        <v>1.084</v>
       </c>
       <c r="D32">
-        <v>1.224</v>
+        <v>1.172</v>
       </c>
       <c r="E32">
-        <v>2.2065080011038</v>
+        <v>1.761149755943273</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>1.183721905632348</v>
+        <v>1.125362206521666</v>
       </c>
       <c r="J32" t="s">
         <v>4</v>
       </c>
       <c r="K32">
-        <v>2.2065080011038</v>
+        <v>1.761149755943273</v>
       </c>
       <c r="L32">
         <v>0.8500971208676269</v>
@@ -1901,25 +1901,25 @@
         <v>59</v>
       </c>
       <c r="C33">
-        <v>0.544</v>
+        <v>0.552</v>
       </c>
       <c r="D33">
-        <v>0.372</v>
+        <v>0.392</v>
       </c>
       <c r="E33">
-        <v>0.2302122475795285</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="F33">
         <v>0.4</v>
       </c>
       <c r="G33">
-        <v>0.4631556872531063</v>
+        <v>0.4767959881424244</v>
       </c>
       <c r="J33" t="s">
         <v>4</v>
       </c>
       <c r="K33">
-        <v>0.2302122475795285</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="L33">
         <v>0.3921195507989373</v>
@@ -1942,25 +1942,25 @@
         <v>59</v>
       </c>
       <c r="C34">
-        <v>10.056</v>
+        <v>10.028</v>
       </c>
       <c r="D34">
-        <v>11.612</v>
+        <v>11.468</v>
       </c>
       <c r="E34">
-        <v>12.72721886527684</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="F34">
         <v>11.6</v>
       </c>
       <c r="G34">
-        <v>10.78735901531492</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="J34" t="s">
         <v>4</v>
       </c>
       <c r="K34">
-        <v>12.72721886527684</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="L34">
         <v>3.050242274051084</v>
@@ -1983,25 +1983,25 @@
         <v>59</v>
       </c>
       <c r="C35">
-        <v>0.656</v>
+        <v>0.632</v>
       </c>
       <c r="D35">
-        <v>0.384</v>
+        <v>0.416</v>
       </c>
       <c r="E35">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F35">
         <v>0.4</v>
       </c>
       <c r="G35">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J35" t="s">
         <v>4</v>
       </c>
       <c r="K35">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L35">
         <v>0.7620693762924241</v>
